--- a/data/trans_camb/POLIPATOLOGIA_5-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_5-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 5,13</t>
+          <t>-1,14; 4,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 5,43</t>
+          <t>-0,6; 5,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 2,09</t>
+          <t>-2,52; 2,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 7,71</t>
+          <t>-1,98; 7,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 12,34</t>
+          <t>1,67; 12,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 3,38</t>
+          <t>-4,17; 2,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 5,06</t>
+          <t>-0,13; 5,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 8,01</t>
+          <t>1,81; 7,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,74</t>
+          <t>-2,43; 1,89</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-45,9; 331,74</t>
+          <t>-38,97; 361,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,31; 407,63</t>
+          <t>-27,36; 424,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-68,7; 178,66</t>
+          <t>-65,93; 166,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,57; 188,63</t>
+          <t>-23,79; 188,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,94; 289,63</t>
+          <t>15,5; 304,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,9; 98,02</t>
+          <t>-46,66; 72,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 154,4</t>
+          <t>-4,78; 169,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,38; 238,18</t>
+          <t>32,0; 248,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-40,46; 55,53</t>
+          <t>-43,14; 60,9</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 4,92</t>
+          <t>-0,58; 4,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 0,11</t>
+          <t>-3,69; 0,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 5,42</t>
+          <t>0,06; 5,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 1,61</t>
+          <t>-6,02; 1,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,65; -1,89</t>
+          <t>-8,81; -2,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 5,79</t>
+          <t>-1,46; 6,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 2,24</t>
+          <t>-2,52; 2,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,78; -1,47</t>
+          <t>-5,8; -1,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 4,79</t>
+          <t>-0,1; 4,74</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,27; 252,32</t>
+          <t>-19,28; 242,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-82,95; 20,93</t>
+          <t>-81,95; 15,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 268,89</t>
+          <t>-6,2; 271,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-45,0; 17,33</t>
+          <t>-43,83; 21,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,21; -19,26</t>
+          <t>-66,73; -19,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 60,91</t>
+          <t>-11,06; 64,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,53; 37,74</t>
+          <t>-29,53; 34,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-65,86; -22,31</t>
+          <t>-66,35; -26,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 78,56</t>
+          <t>-1,48; 74,19</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 4,47</t>
+          <t>-0,25; 4,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,99</t>
+          <t>-1,5; 1,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,65; 14,51</t>
+          <t>7,88; 14,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,65; 9,79</t>
+          <t>2,73; 10,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 7,28</t>
+          <t>0,83; 7,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,35; 18,05</t>
+          <t>11,52; 18,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,77; 6,31</t>
+          <t>1,87; 5,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,1</t>
+          <t>0,37; 4,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,81; 15,55</t>
+          <t>10,63; 15,44</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-47,18; 850,25</t>
+          <t>-39,17; 1156,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-75,24; 495,11</t>
+          <t>-79,05; 584,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>310,95; 3978,62</t>
+          <t>294,83; 3856,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>57,74; 720,14</t>
+          <t>52,93; 805,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,76; 566,38</t>
+          <t>12,37; 595,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>284,33; 1389,51</t>
+          <t>281,09; 1605,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>65,35; 583,36</t>
+          <t>61,35; 488,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,09; 373,65</t>
+          <t>10,98; 362,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>392,75; 1603,86</t>
+          <t>372,84; 1446,05</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 4,36</t>
+          <t>-1,16; 4,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 5,73</t>
+          <t>-0,12; 5,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,37; 12,25</t>
+          <t>4,65; 12,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,29; 14,29</t>
+          <t>6,38; 14,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,32; 13,48</t>
+          <t>4,97; 13,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,53; 13,34</t>
+          <t>3,18; 13,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,15; 8,35</t>
+          <t>3,35; 8,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,36; 8,48</t>
+          <t>3,29; 8,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,04; 11,57</t>
+          <t>5,28; 11,71</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-37,65; 290,72</t>
+          <t>-35,23; 294,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 385,38</t>
+          <t>-12,62; 409,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>94,72; 828,54</t>
+          <t>105,41; 822,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>107,01; 530,06</t>
+          <t>102,87; 524,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>90,78; 516,81</t>
+          <t>84,26; 449,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>63,85; 448,28</t>
+          <t>58,86; 454,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>69,67; 318,64</t>
+          <t>70,86; 333,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>68,56; 315,56</t>
+          <t>70,98; 331,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>117,25; 468,29</t>
+          <t>127,56; 469,96</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,34; 11,29</t>
+          <t>2,21; 11,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 6,07</t>
+          <t>-0,87; 5,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,92; 11,6</t>
+          <t>3,57; 11,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,47; 18,98</t>
+          <t>6,31; 18,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 10,45</t>
+          <t>0,68; 11,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,85; 15,13</t>
+          <t>0,06; 14,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,34; 13,4</t>
+          <t>5,68; 13,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,01</t>
+          <t>0,66; 7,39</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,21; 12,45</t>
+          <t>4,19; 12,53</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>35,82; 1037,19</t>
+          <t>24,77; 939,01</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-46,2; 615,87</t>
+          <t>-38,42; 532,32</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>72,96; 1263,78</t>
+          <t>63,88; 1235,74</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>63,0; 653,87</t>
+          <t>66,88; 706,52</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 382,24</t>
+          <t>-4,9; 473,09</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,65; 519,52</t>
+          <t>7,61; 511,26</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,16; 558,45</t>
+          <t>101,76; 565,27</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>10,73; 309,53</t>
+          <t>6,76; 330,93</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>86,0; 556,2</t>
+          <t>78,26; 516,95</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,71</t>
+          <t>2,96; 8,37</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,47</t>
+          <t>1,95; 6,73</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13,65; 20,47</t>
+          <t>13,75; 20,67</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 6,0</t>
+          <t>-1,37; 6,74</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 6,79</t>
+          <t>-1,47; 6,59</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,56; 27,97</t>
+          <t>18,33; 28,12</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,13</t>
+          <t>1,31; 5,89</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,26</t>
+          <t>0,68; 5,46</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>17,11; 22,94</t>
+          <t>16,96; 22,96</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-28,78; 238,53</t>
+          <t>-26,37; 254,63</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-35,1; 269,73</t>
+          <t>-29,0; 266,95</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>265,77; 1122,46</t>
+          <t>265,75; 1267,24</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>30,44; 461,5</t>
+          <t>34,86; 446,79</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6,74; 374,52</t>
+          <t>9,64; 393,05</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>474,56; 1876,04</t>
+          <t>464,09; 1741,79</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,85</t>
+          <t>-1,89; 2,03</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,93</t>
+          <t>-1,15; 3,01</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,62; 9,04</t>
+          <t>3,72; 9,13</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,12; 7,05</t>
+          <t>1,24; 6,97</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,77; 7,67</t>
+          <t>2,05; 7,93</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,08; 62,71</t>
+          <t>15,81; 65,44</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,07</t>
+          <t>0,36; 3,93</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,94</t>
+          <t>1,16; 4,88</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>10,98; 52,27</t>
+          <t>11,03; 49,13</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-50,06; 82,06</t>
+          <t>-46,72; 95,79</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-29,47; 124,08</t>
+          <t>-30,67; 135,68</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>87,2; 393,65</t>
+          <t>75,94; 383,2</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15,74; 161,13</t>
+          <t>16,63; 153,15</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>24,0; 178,48</t>
+          <t>27,4; 177,87</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>257,51; 1691,69</t>
+          <t>248,08; 1423,22</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,71; 111,76</t>
+          <t>5,82; 106,39</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>22,14; 131,93</t>
+          <t>20,14; 130,68</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>227,5; 1293,62</t>
+          <t>225,75; 1332,28</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-7,43; -3,29</t>
+          <t>-7,16; -3,22</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,82; -1,48</t>
+          <t>-5,96; -1,41</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 0,62</t>
+          <t>-5,97; 0,48</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 2,47</t>
+          <t>-3,71; 2,15</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 5,27</t>
+          <t>-1,01; 5,13</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,52; 7,86</t>
+          <t>1,37; 7,37</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,62; -1,02</t>
+          <t>-4,72; -1,06</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 1,44</t>
+          <t>-2,56; 1,33</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 2,75</t>
+          <t>-2,94; 2,84</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-86,7; -53,91</t>
+          <t>-86,26; -53,89</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-68,99; -20,23</t>
+          <t>-69,75; -22,17</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-73,61; 8,32</t>
+          <t>-72,91; 6,66</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-33,8; 35,61</t>
+          <t>-35,13; 30,71</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 74,02</t>
+          <t>-10,74; 68,47</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,62; 104,52</t>
+          <t>11,85; 101,25</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-51,49; -14,42</t>
+          <t>-52,11; -14,6</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-28,72; 20,61</t>
+          <t>-29,16; 19,2</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-34,38; 37,79</t>
+          <t>-33,16; 37,73</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,28</t>
+          <t>-0,56; 1,35</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,95</t>
+          <t>-0,78; 1,03</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,77</t>
+          <t>2,78; 5,8</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,41</t>
+          <t>1,87; 4,54</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,49</t>
+          <t>1,81; 4,62</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,92; 29,05</t>
+          <t>8,93; 28,94</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,59</t>
+          <t>0,95; 2,62</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,41</t>
+          <t>0,82; 2,48</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>6,48; 18,45</t>
+          <t>6,57; 17,29</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 44,02</t>
+          <t>-15,15; 45,52</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-20,1; 30,97</t>
+          <t>-20,25; 34,15</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>78,76; 191,5</t>
+          <t>78,94; 196,21</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>24,02; 71,98</t>
+          <t>25,54; 75,25</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>21,43; 73,04</t>
+          <t>23,98; 74,54</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>127,37; 449,22</t>
+          <t>128,89; 452,83</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>16,33; 54,18</t>
+          <t>16,94; 56,79</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>13,87; 51,36</t>
+          <t>14,34; 51,64</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>124,87; 367,06</t>
+          <t>126,3; 341,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/POLIPATOLOGIA_5-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_5-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,15</t>
+          <t>-0,1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>-0,18</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>-0,11</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 4,96</t>
+          <t>-1,06; 4,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 5,64</t>
+          <t>-0,99; 5,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 2,09</t>
+          <t>-2,47; 2,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 7,76</t>
+          <t>-2,22; 8,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 12,24</t>
+          <t>1,81; 12,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 2,99</t>
+          <t>-4,42; 2,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 5,3</t>
+          <t>-0,24; 5,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 7,66</t>
+          <t>1,95; 8,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,89</t>
+          <t>-2,29; 2,01</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-5,89%</t>
+          <t>-3,97%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-3,76%</t>
+          <t>-2,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-4,95%</t>
+          <t>-2,51%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,97; 361,77</t>
+          <t>-35,67; 364,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,36; 424,37</t>
+          <t>-32,33; 355,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-65,93; 166,98</t>
+          <t>-67,17; 153,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,79; 188,35</t>
+          <t>-28,55; 195,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,5; 304,04</t>
+          <t>13,42; 288,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,66; 72,34</t>
+          <t>-49,11; 67,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 169,08</t>
+          <t>-7,0; 181,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,0; 248,26</t>
+          <t>35,78; 276,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-43,14; 60,9</t>
+          <t>-39,24; 63,74</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,57</t>
+          <t>2,81</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,2</t>
+          <t>2,04</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,33</t>
+          <t>2,44</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 4,6</t>
+          <t>-0,7; 4,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 0,15</t>
+          <t>-3,79; 0,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 5,56</t>
+          <t>0,02; 5,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 1,85</t>
+          <t>-5,8; 2,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,81; -2,04</t>
+          <t>-9,47; -1,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 6,22</t>
+          <t>-1,8; 5,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 2,16</t>
+          <t>-2,31; 2,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,8; -1,74</t>
+          <t>-5,59; -1,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 4,74</t>
+          <t>0,19; 4,8</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>33,1%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,28; 242,38</t>
+          <t>-21,54; 222,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-81,95; 15,88</t>
+          <t>-81,08; 16,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 271,99</t>
+          <t>-4,82; 266,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,83; 21,95</t>
+          <t>-43,67; 26,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,73; -19,45</t>
+          <t>-70,09; -20,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 64,06</t>
+          <t>-12,88; 55,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,53; 34,47</t>
+          <t>-28,02; 41,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,35; -26,62</t>
+          <t>-66,83; -25,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 74,19</t>
+          <t>2,35; 81,09</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10,96</t>
+          <t>11,35</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,78</t>
+          <t>14,65</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12,98</t>
+          <t>13,12</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 4,44</t>
+          <t>-0,22; 4,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,97</t>
+          <t>-1,32; 1,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,88; 14,23</t>
+          <t>8,45; 15,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,73; 10,05</t>
+          <t>2,35; 9,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 7,13</t>
+          <t>0,63; 7,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,52; 18,66</t>
+          <t>11,17; 18,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,89</t>
+          <t>1,66; 6,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,07</t>
+          <t>0,27; 4,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,63; 15,44</t>
+          <t>10,82; 15,73</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>935,09%</t>
+          <t>967,92%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>612,5%</t>
+          <t>606,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>717,83%</t>
+          <t>725,3%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-39,17; 1156,03</t>
+          <t>-37,25; 1034,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-79,05; 584,99</t>
+          <t>-74,66; 412,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>294,83; 3856,48</t>
+          <t>318,14; 4394,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52,93; 805,36</t>
+          <t>49,65; 783,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,37; 595,84</t>
+          <t>4,58; 495,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>281,09; 1605,84</t>
+          <t>267,64; 1543,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>61,35; 488,97</t>
+          <t>56,81; 576,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,98; 362,34</t>
+          <t>1,41; 370,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>372,84; 1446,05</t>
+          <t>360,32; 1488,84</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8,11</t>
+          <t>7,1</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,95</t>
+          <t>11,63</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8,77</t>
+          <t>9,54</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 4,37</t>
+          <t>-1,01; 4,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 5,82</t>
+          <t>0,05; 5,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,65; 12,17</t>
+          <t>3,99; 10,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,38; 14,27</t>
+          <t>5,91; 14,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,97; 13,69</t>
+          <t>5,22; 13,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 13,24</t>
+          <t>8,32; 14,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,35; 8,49</t>
+          <t>3,38; 8,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,29; 8,43</t>
+          <t>3,66; 8,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,28; 11,71</t>
+          <t>7,2; 11,99</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>315,42%</t>
+          <t>275,88%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>211,76%</t>
+          <t>275,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>257,04%</t>
+          <t>279,47%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-35,23; 294,58</t>
+          <t>-32,4; 353,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 409,07</t>
+          <t>-7,87; 409,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>105,41; 822,78</t>
+          <t>83,06; 752,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>102,87; 524,23</t>
+          <t>94,0; 514,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>84,26; 449,72</t>
+          <t>89,39; 534,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>58,86; 454,43</t>
+          <t>125,7; 498,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,86; 333,32</t>
+          <t>70,25; 329,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>70,98; 331,76</t>
+          <t>80,28; 348,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>127,56; 469,96</t>
+          <t>150,48; 487,84</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7,38</t>
+          <t>6,54</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,9</t>
+          <t>12,21</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9,11</t>
+          <t>9,59</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,21; 11,34</t>
+          <t>2,16; 11,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 5,75</t>
+          <t>-0,91; 6,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,57; 11,14</t>
+          <t>2,88; 10,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,31; 18,85</t>
+          <t>6,81; 18,11</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 11,26</t>
+          <t>0,59; 11,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 14,98</t>
+          <t>6,52; 16,35</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,68; 13,48</t>
+          <t>5,74; 12,81</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,66; 7,39</t>
+          <t>0,66; 6,91</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,19; 12,53</t>
+          <t>6,38; 12,39</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>323,77%</t>
+          <t>286,72%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>196,73%</t>
+          <t>242,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>248,14%</t>
+          <t>261,19%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>24,77; 939,01</t>
+          <t>21,33; 1168,25</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-38,42; 532,32</t>
+          <t>-40,45; 689,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>63,88; 1235,74</t>
+          <t>52,38; 995,97</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>66,88; 706,52</t>
+          <t>80,29; 648,44</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 473,09</t>
+          <t>-3,02; 396,47</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,61; 511,26</t>
+          <t>73,67; 618,91</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>101,76; 565,27</t>
+          <t>108,19; 549,13</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>6,76; 330,93</t>
+          <t>8,64; 277,77</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>78,26; 516,95</t>
+          <t>103,2; 551,72</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16,94</t>
+          <t>16,92</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,47</t>
+          <t>23,58</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>20,04</t>
+          <t>20,15</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,96; 8,37</t>
+          <t>2,64; 7,95</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,73</t>
+          <t>1,85; 6,48</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13,75; 20,67</t>
+          <t>13,37; 20,59</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 6,74</t>
+          <t>-1,45; 6,17</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 6,59</t>
+          <t>-1,89; 6,28</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,33; 28,12</t>
+          <t>18,78; 28,16</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,31; 5,89</t>
+          <t>1,12; 6,49</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,46</t>
+          <t>0,71; 5,32</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>16,96; 22,96</t>
+          <t>17,17; 23,28</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>541,23%</t>
+          <t>543,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>912,3%</t>
+          <t>917,04%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-26,37; 254,63</t>
+          <t>-30,12; 254,05</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-29,0; 266,95</t>
+          <t>-34,49; 220,39</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>265,75; 1267,24</t>
+          <t>261,76; 1104,88</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>34,86; 446,79</t>
+          <t>25,27; 489,42</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>9,64; 393,05</t>
+          <t>14,54; 407,78</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>464,09; 1741,79</t>
+          <t>466,87; 1828,74</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6,22</t>
+          <t>6,16</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>35,66</t>
+          <t>16,85</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>23,36</t>
+          <t>11,72</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 2,03</t>
+          <t>-2,06; 1,92</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,01</t>
+          <t>-1,1; 3,23</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,72; 9,13</t>
+          <t>3,66; 8,79</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,24; 6,97</t>
+          <t>1,02; 6,93</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,05; 7,93</t>
+          <t>1,87; 7,87</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,81; 65,44</t>
+          <t>13,44; 19,95</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,93</t>
+          <t>0,28; 3,88</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,88</t>
+          <t>1,31; 4,91</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>11,03; 49,13</t>
+          <t>9,76; 13,91</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>193,35%</t>
+          <t>191,45%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>614,27%</t>
+          <t>290,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>515,16%</t>
+          <t>258,32%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-46,72; 95,79</t>
+          <t>-49,45; 89,2</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-30,67; 135,68</t>
+          <t>-27,89; 150,57</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>75,94; 383,2</t>
+          <t>83,95; 389,8</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>16,63; 153,15</t>
+          <t>12,19; 153,21</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>27,4; 177,87</t>
+          <t>22,95; 171,49</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>248,08; 1423,22</t>
+          <t>178,58; 449,65</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,82; 106,39</t>
+          <t>4,65; 99,75</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>20,14; 130,68</t>
+          <t>24,04; 128,19</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>225,75; 1332,28</t>
+          <t>173,21; 372,67</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-2,19</t>
+          <t>-0,7</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,49</t>
+          <t>3,65</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>1,51</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-7,16; -3,22</t>
+          <t>-7,29; -3,16</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,96; -1,41</t>
+          <t>-5,69; -1,32</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 0,48</t>
+          <t>-3,0; 1,9</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 2,15</t>
+          <t>-3,67; 2,17</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 5,13</t>
+          <t>-1,38; 5,18</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,37; 7,37</t>
+          <t>0,85; 6,41</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,72; -1,06</t>
+          <t>-4,73; -1,22</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,33</t>
+          <t>-2,6; 1,15</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 2,84</t>
+          <t>-0,44; 3,35</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-31,42%</t>
+          <t>-10,07%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-86,26; -53,89</t>
+          <t>-85,96; -52,19</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-69,75; -22,17</t>
+          <t>-70,48; -20,95</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-72,91; 6,66</t>
+          <t>-35,55; 33,28</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-35,13; 30,71</t>
+          <t>-35,4; 28,87</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 68,47</t>
+          <t>-13,49; 68,92</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,85; 101,25</t>
+          <t>8,37; 93,35</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-52,11; -14,6</t>
+          <t>-52,02; -17,81</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-29,16; 19,2</t>
+          <t>-29,64; 16,86</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-33,16; 37,73</t>
+          <t>-4,47; 50,15</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4,54</t>
+          <t>4,98</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,99</t>
+          <t>9,68</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>9,47</t>
+          <t>7,42</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,35</t>
+          <t>-0,53; 1,33</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,03</t>
+          <t>-0,85; 0,98</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,8</t>
+          <t>3,94; 6,02</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,54</t>
+          <t>1,84; 4,54</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,62</t>
+          <t>1,67; 4,55</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,93; 28,94</t>
+          <t>8,51; 11,04</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,62</t>
+          <t>0,97; 2,59</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,48</t>
+          <t>0,81; 2,48</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>6,57; 17,29</t>
+          <t>6,55; 8,28</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>133,07%</t>
+          <t>145,98%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>208,71%</t>
+          <t>144,44%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>186,19%</t>
+          <t>145,95%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 45,52</t>
+          <t>-13,54; 45,07</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 34,15</t>
+          <t>-22,21; 31,12</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>78,94; 196,21</t>
+          <t>100,2; 199,14</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>25,54; 75,25</t>
+          <t>24,72; 74,38</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>23,98; 74,54</t>
+          <t>22,99; 75,2</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>128,89; 452,83</t>
+          <t>113,29; 181,88</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>16,94; 56,79</t>
+          <t>17,67; 54,64</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>14,34; 51,64</t>
+          <t>14,82; 52,58</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>126,3; 341,95</t>
+          <t>119,33; 179,06</t>
         </is>
       </c>
     </row>
